--- a/business_surveys/032_decode_e_numbers_survey--business_surveys.xlsx
+++ b/business_surveys/032_decode_e_numbers_survey--business_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,7 +515,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>concerns</t>
+          <t>e_numbers_use</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Concerns</t>
+          <t>How do you currently use E-numbers in your work?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>e_numbers_awareness_2</t>
+          <t>concerns</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>E Numbers Awareness</t>
+          <t>Concerns</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>e_numbers_awareness_2</t>
+          <t>e_numbers_importance</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>E Numbers Awareness</t>
+          <t>How important is E-numbers awareness in your business decisions?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,16 +612,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>concerns_2</t>
+          <t>awareness_improvement</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Concerns</t>
+          <t>How do you think your business could improve E-numbers awareness?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>select_one</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>alternative_solutions</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Are you currently using alternative solutions or alternatives to E-numbers?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -638,7 +661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -688,12 +711,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>e-numbers</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>E-numbers</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -705,12 +728,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>e-numbers</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>E-numbers</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -722,403 +745,63 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>e-numbers</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>E-numbers</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>e_numbers_awareness_choices</t>
+          <t>alternative_solutions_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>e-numbers</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>E-numbers</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>e_numbers_awareness_choices</t>
+          <t>alternative_solutions_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>e-numbers</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>E-numbers</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>e_numbers_awareness_choices</t>
+          <t>alternative_solutions_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>e-numbers</t>
+          <t>undecided</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>E-numbers</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>e_numbers_awareness_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>e-numbers</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>E-numbers</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>e_numbers_awareness_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>e-numbers</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>E-numbers</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>e_numbers_awareness_2_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>e-numbers</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>E-numbers</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>e_numbers_awareness_2_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>e-numbers</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>E-numbers</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>e_numbers_awareness_2_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>e-numbers</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>E-numbers</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>e_numbers_awareness_2_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>e-numbers</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>E-numbers</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>e_numbers_awareness_2_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>e-numbers</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>E-numbers</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>e_numbers_awareness_2_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>e-numbers</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>E-numbers</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>e_numbers_awareness_2_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>e-numbers</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>E-numbers</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>e_numbers_awareness_2_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>e-numbers</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>E-numbers</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>e_numbers_awareness_2_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>e-numbers</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>E-numbers</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>e_numbers_awareness_2_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>e-numbers</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>E-numbers</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>e_numbers_awareness_2_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>e-numbers</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>E-numbers</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>e_numbers_awareness_2_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>e-numbers</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>E-numbers</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>e_numbers_awareness_2_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>e-numbers</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>E-numbers</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>e_numbers_awareness_2_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>e-numbers</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>E-numbers</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>e_numbers_awareness_2_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>e-numbers</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>E-numbers</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>e_numbers_awareness_2_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>e-numbers</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>E-numbers</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>e_numbers_awareness_2_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>e-numbers</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>E-numbers</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>e_numbers_awareness_2_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>e-numbers</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>E-numbers</t>
+          <t>Undecided</t>
         </is>
       </c>
     </row>
